--- a/storage/app/assessTemplate/sun.xlsx
+++ b/storage/app/assessTemplate/sun.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\excel\評価シートテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13C5C85-D00C-4D80-B85B-5AD6BEBD76A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD711C4-A8ED-42DB-B8CF-6516444017DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{C12BCA10-30F3-4130-A46E-AF6E177374E9}"/>
+    <workbookView xWindow="45" yWindow="765" windowWidth="28755" windowHeight="15435" xr2:uid="{C12BCA10-30F3-4130-A46E-AF6E177374E9}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（太陽光付）" sheetId="2" r:id="rId1"/>
@@ -374,7 +374,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="#,##0.0;[Red]\-#,##0.0"/>
     <numFmt numFmtId="177" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="178" formatCode="#,##0&quot;千円&quot;"/>
@@ -383,6 +383,7 @@
     <numFmt numFmtId="181" formatCode="#,##0.00&quot;㎡&quot;"/>
     <numFmt numFmtId="182" formatCode="#,##0.00&quot;千円&quot;"/>
     <numFmt numFmtId="183" formatCode="0;_ꐀ"/>
+    <numFmt numFmtId="184" formatCode="ggge&quot;年&quot;"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1286,6 +1287,69 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1363,74 +1427,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1777,8 +1778,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,47 +1789,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="86"/>
-      <c r="K4" s="87"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="L4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="84"/>
-      <c r="N4" s="88"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="107"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1836,8 +1837,8 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1866,12 +1867,12 @@
     </row>
     <row r="7" spans="1:15" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="90"/>
-      <c r="C7" s="91"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="95"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="110"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="112"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="114"/>
       <c r="J7" s="15" t="s">
         <v>10</v>
       </c>
@@ -1990,10 +1991,10 @@
     </row>
     <row r="15" spans="1:15" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="14"/>
-      <c r="B15" s="76"/>
-      <c r="C15" s="77"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="79"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="96"/>
+      <c r="E15" s="97"/>
+      <c r="F15" s="98"/>
       <c r="H15" s="24"/>
       <c r="I15" s="25"/>
       <c r="J15" s="26"/>
@@ -2012,23 +2013,23 @@
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="E17" s="103" t="s">
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="E17" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="96" t="s">
+      <c r="G17" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="97"/>
+      <c r="H17" s="83"/>
       <c r="I17" s="33" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="96" t="s">
+      <c r="K17" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="L17" s="97"/>
+      <c r="L17" s="83"/>
       <c r="M17" s="33" t="s">
         <v>21</v>
       </c>
@@ -2036,9 +2037,9 @@
     </row>
     <row r="18" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="11"/>
-      <c r="B18" s="102"/>
-      <c r="C18" s="102"/>
-      <c r="E18" s="104"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="E18" s="92"/>
       <c r="G18" s="34" t="s">
         <v>23</v>
       </c>
@@ -2066,11 +2067,11 @@
         <v>26</v>
       </c>
       <c r="C19" s="38"/>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="98" t="s">
+      <c r="E19" s="93"/>
+      <c r="F19" s="86" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="39"/>
@@ -2088,9 +2089,9 @@
         <v>29</v>
       </c>
       <c r="C20" s="38"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="98"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="86"/>
       <c r="G20" s="43"/>
       <c r="H20" s="44"/>
       <c r="I20" s="44"/>
@@ -2106,9 +2107,9 @@
         <v>30</v>
       </c>
       <c r="C21" s="38"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="98"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="86"/>
       <c r="G21" s="45"/>
       <c r="H21" s="46"/>
       <c r="I21" s="46"/>
@@ -2124,21 +2125,21 @@
     </row>
     <row r="23" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="11"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="101" t="s">
+      <c r="B23" s="89"/>
+      <c r="C23" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="103" t="s">
+      <c r="E23" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="109" t="s">
+      <c r="G23" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="110"/>
-      <c r="K23" s="96" t="s">
+      <c r="H23" s="81"/>
+      <c r="K23" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="L23" s="97"/>
+      <c r="L23" s="83"/>
       <c r="M23" s="33" t="s">
         <v>21</v>
       </c>
@@ -2146,9 +2147,9 @@
     </row>
     <row r="24" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="11"/>
-      <c r="B24" s="102"/>
-      <c r="C24" s="102"/>
-      <c r="E24" s="104"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
+      <c r="E24" s="92"/>
       <c r="G24" s="47"/>
       <c r="H24" s="35" t="s">
         <v>35</v>
@@ -2168,11 +2169,11 @@
         <v>26</v>
       </c>
       <c r="C25" s="48"/>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="113"/>
-      <c r="F25" s="98" t="s">
+      <c r="E25" s="87"/>
+      <c r="F25" s="86" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="49"/>
@@ -2190,9 +2191,9 @@
         <v>29</v>
       </c>
       <c r="C26" s="48"/>
-      <c r="D26" s="98"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="98"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="86"/>
       <c r="G26" s="52"/>
       <c r="H26" s="53"/>
       <c r="I26" s="51"/>
@@ -2208,9 +2209,9 @@
         <v>30</v>
       </c>
       <c r="C27" s="48"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="98"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="86"/>
       <c r="G27" s="54"/>
       <c r="H27" s="55"/>
       <c r="I27" s="51"/>
@@ -2247,86 +2248,86 @@
       <c r="A30" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="111"/>
-      <c r="C30" s="111"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="111"/>
-      <c r="N30" s="112"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
       <c r="O30" s="20"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="65"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="106"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="76"/>
+      <c r="N31" s="77"/>
       <c r="O31" s="20"/>
     </row>
     <row r="32" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="65"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="105"/>
-      <c r="J32" s="105"/>
-      <c r="K32" s="105"/>
-      <c r="L32" s="105"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="106"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="76"/>
+      <c r="M32" s="76"/>
+      <c r="N32" s="77"/>
       <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="11"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="105"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="105"/>
-      <c r="J33" s="105"/>
-      <c r="K33" s="105"/>
-      <c r="L33" s="105"/>
-      <c r="M33" s="105"/>
-      <c r="N33" s="106"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="76"/>
+      <c r="L33" s="76"/>
+      <c r="M33" s="76"/>
+      <c r="N33" s="77"/>
     </row>
     <row r="34" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="66"/>
-      <c r="B34" s="107"/>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="107"/>
-      <c r="G34" s="107"/>
-      <c r="H34" s="107"/>
-      <c r="I34" s="107"/>
-      <c r="J34" s="107"/>
-      <c r="K34" s="107"/>
-      <c r="L34" s="107"/>
-      <c r="M34" s="107"/>
-      <c r="N34" s="108"/>
+      <c r="B34" s="78"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="78"/>
+      <c r="M34" s="78"/>
+      <c r="N34" s="79"/>
     </row>
     <row r="35" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="64"/>
@@ -2402,27 +2403,6 @@
     <row r="77" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="L1:M1"/>
@@ -2436,6 +2416,27 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">

--- a/storage/app/assessTemplate/sun.xlsx
+++ b/storage/app/assessTemplate/sun.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\assessTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD711C4-A8ED-42DB-B8CF-6516444017DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F37C4F-BC82-40A2-80B9-63F619EFB851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="765" windowWidth="28755" windowHeight="15435" xr2:uid="{C12BCA10-30F3-4130-A46E-AF6E177374E9}"/>
+    <workbookView xWindow="45" yWindow="45" windowWidth="28755" windowHeight="15435" xr2:uid="{C12BCA10-30F3-4130-A46E-AF6E177374E9}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（太陽光付）" sheetId="2" r:id="rId1"/>
@@ -1287,22 +1287,6 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1314,14 +1298,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1433,6 +1409,30 @@
     </xf>
     <xf numFmtId="184" fontId="7" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1778,8 +1778,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1789,47 +1789,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="100"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
       <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
       <c r="I4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="105"/>
-      <c r="K4" s="106"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="100"/>
       <c r="L4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="103"/>
-      <c r="N4" s="107"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="101"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1837,8 +1837,8 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1867,17 +1867,17 @@
     </row>
     <row r="7" spans="1:15" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="109"/>
-      <c r="C7" s="110"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="112"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="104"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="106"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="108"/>
       <c r="J7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="115"/>
-      <c r="L7" s="116"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="110"/>
       <c r="N7" s="13"/>
     </row>
     <row r="8" spans="1:15" ht="14.25" hidden="1" x14ac:dyDescent="0.4">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15" spans="1:15" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="14"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="96"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="98"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="92"/>
       <c r="H15" s="24"/>
       <c r="I15" s="25"/>
       <c r="J15" s="26"/>
@@ -2013,23 +2013,23 @@
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="E17" s="91" t="s">
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="E17" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="83"/>
+      <c r="H17" s="79"/>
       <c r="I17" s="33" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="82" t="s">
+      <c r="K17" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="L17" s="83"/>
+      <c r="L17" s="79"/>
       <c r="M17" s="33" t="s">
         <v>21</v>
       </c>
@@ -2037,9 +2037,9 @@
     </row>
     <row r="18" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="11"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
-      <c r="E18" s="92"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="84"/>
+      <c r="E18" s="86"/>
       <c r="G18" s="34" t="s">
         <v>23</v>
       </c>
@@ -2067,11 +2067,11 @@
         <v>26</v>
       </c>
       <c r="C19" s="38"/>
-      <c r="D19" s="86" t="s">
+      <c r="D19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="93"/>
-      <c r="F19" s="86" t="s">
+      <c r="E19" s="87"/>
+      <c r="F19" s="80" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="39"/>
@@ -2089,9 +2089,9 @@
         <v>29</v>
       </c>
       <c r="C20" s="38"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="86"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="80"/>
       <c r="G20" s="43"/>
       <c r="H20" s="44"/>
       <c r="I20" s="44"/>
@@ -2107,9 +2107,9 @@
         <v>30</v>
       </c>
       <c r="C21" s="38"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="86"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="80"/>
       <c r="G21" s="45"/>
       <c r="H21" s="46"/>
       <c r="I21" s="46"/>
@@ -2125,21 +2125,21 @@
     </row>
     <row r="23" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="11"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89" t="s">
+      <c r="B23" s="83"/>
+      <c r="C23" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="91" t="s">
+      <c r="E23" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="80" t="s">
+      <c r="G23" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="81"/>
-      <c r="K23" s="82" t="s">
+      <c r="H23" s="77"/>
+      <c r="K23" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="L23" s="83"/>
+      <c r="L23" s="79"/>
       <c r="M23" s="33" t="s">
         <v>21</v>
       </c>
@@ -2147,9 +2147,9 @@
     </row>
     <row r="24" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="11"/>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="E24" s="92"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="84"/>
+      <c r="E24" s="86"/>
       <c r="G24" s="47"/>
       <c r="H24" s="35" t="s">
         <v>35</v>
@@ -2169,11 +2169,11 @@
         <v>26</v>
       </c>
       <c r="C25" s="48"/>
-      <c r="D25" s="86" t="s">
+      <c r="D25" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="87"/>
-      <c r="F25" s="86" t="s">
+      <c r="E25" s="81"/>
+      <c r="F25" s="80" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="49"/>
@@ -2191,9 +2191,9 @@
         <v>29</v>
       </c>
       <c r="C26" s="48"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="86"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="80"/>
       <c r="G26" s="52"/>
       <c r="H26" s="53"/>
       <c r="I26" s="51"/>
@@ -2209,9 +2209,9 @@
         <v>30</v>
       </c>
       <c r="C27" s="48"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="86"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="80"/>
       <c r="G27" s="54"/>
       <c r="H27" s="55"/>
       <c r="I27" s="51"/>
@@ -2248,86 +2248,86 @@
       <c r="A30" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="85"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="112"/>
       <c r="O30" s="20"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="65"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="77"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="114"/>
       <c r="O31" s="20"/>
     </row>
     <row r="32" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="65"/>
-      <c r="B32" s="76"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
-      <c r="M32" s="76"/>
-      <c r="N32" s="77"/>
+      <c r="B32" s="113"/>
+      <c r="C32" s="113"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="113"/>
+      <c r="M32" s="113"/>
+      <c r="N32" s="114"/>
       <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="11"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="76"/>
-      <c r="N33" s="77"/>
+      <c r="B33" s="113"/>
+      <c r="C33" s="113"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="113"/>
+      <c r="N33" s="114"/>
     </row>
     <row r="34" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="66"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="78"/>
-      <c r="N34" s="79"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="115"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="115"/>
+      <c r="J34" s="115"/>
+      <c r="K34" s="115"/>
+      <c r="L34" s="115"/>
+      <c r="M34" s="115"/>
+      <c r="N34" s="116"/>
     </row>
     <row r="35" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="64"/>
@@ -2402,7 +2402,7 @@
     <row r="71" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="77" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="30">
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="L1:M1"/>
@@ -2416,24 +2416,20 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="B30:N34"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="E23:E24"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="E25:E27"/>
     <mergeCell ref="F25:F27"/>
